--- a/parity/fixtures/quarterly-sales-dashboard.xlsx
+++ b/parity/fixtures/quarterly-sales-dashboard.xlsx
@@ -750,7 +750,7 @@
     </tableColumn>
     <tableColumn id="7" name="Growth" totalsRowFunction="custom" dataDxfId="1">
       <calculatedColumnFormula>SalesTable[[#This Row],Q4]/SalesTable[[#This Row],Q1]-1</calculatedColumnFormula>
-      <totalsRowFormula>custom</totalsRowFormula>
+      <totalsRowFormula>SUBTOTAL(109,[Q4])/SUBTOTAL(109,[Q1])-1</totalsRowFormula>
     </tableColumn>
     <tableColumn id="8" name="Trend"/>
   </tableColumns>
@@ -1263,8 +1263,8 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f>custom</f>
-        <v>0.277</v>
+        <f>SUBTOTAL(109,[Q4])/SUBTOTAL(109,[Q1])-1</f>
+        <v>0.2997</v>
       </c>
     </row>
     <row r="14" spans="2:9">
